--- a/ZKD-Feature-Checklist.xlsx
+++ b/ZKD-Feature-Checklist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Feature checklist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Member scenarios" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature checklist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Member scenarios" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feature checklist'!$A$1:$H$44</definedName>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>REAL logic, MOCK data</t>
+          <t>MOSTLY REAL - I verified this live</t>
         </is>
       </c>
       <c r="E17" s="16" t="inlineStr">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="G17" s="16" t="inlineStr">
         <is>
-          <t>duffel/kiwi/skyscanner/sabre/travelport/travelfusion each with a status</t>
+          <t>duffel=real sandbox, oag=real, liteapi(hotel)=real registered supplier, ground(Uber)=real sandbox OAuth2; kiwi/skyscanner/sabre/travelfusion no-key</t>
         </is>
       </c>
       <c r="H17" s="16" t="inlineStr">
         <is>
-          <t>Most say 'no-key' and return NOTHING (not fake data). Travelport is synthetic and flagged live:false</t>
+          <t>Corrected 2026-08-21 (was 'REAL logic, MOCK data' for all of ground/hotel - stale since 2026-08-19). Only kiwi/skyscanner/travelfusion return nothing without a key; Travelport is synthetic and flagged live:false; sabre cert returns no inventory</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>Cabin entitlement, preferred carriers, per-transaction cap (Rs 25,000)</t>
+          <t>Cabin entitlement, preferred carriers, outOfPocketCap (a soft input to hotel-affordability/ground checks, NOT an enforced spend ceiling since 2026-08-19)</t>
         </is>
       </c>
       <c r="H22" s="16" t="inlineStr">
         <is>
-          <t>MOCKED - there is no MYCA_API_KEY, so every member gets the same profile. Labelled source:'mock'</t>
+          <t>MOCKED - there is no MYCA_API_KEY, so every member gets the same profile, source:'mock'. Corrected 2026-08-21: the Rs 25,000 per-transaction CAP this row used to describe as enforced was removed 2026-08-19 - see row 46 below</t>
         </is>
       </c>
     </row>
@@ -2265,27 +2265,27 @@
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>NOT BUILT (deliberately)</t>
+          <t>REAL - I verified this live</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>not built</t>
+          <t>server/webhooks/, server/engine/statusPoller.ts, server/engine/memberReports.ts</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Open /ops and check the per-lane liveness heartbeat; or POST a real webhook payload with curl</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Three lanes: push (Duffel/AeroDataBox), poll (AviationStack fallback, 15/mo ceiling), member report (3-corroborator threshold)</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>A poller was designed and budgeted but never written. /ops stands in for it</t>
+          <t>Corrected 2026-08-21 - built 2026-08-19, this row was stale. OAG's own webhook is still deliberately stubbed inert pending a subscription; Duffel's webhook fires for nothing since no PNR here originates through Duffel</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C47" s="23" t="inlineStr">
         <is>
-          <t>REAL logic, MOCK data</t>
+          <t>REAL logic, MOCK settlement</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
-          <t>Refunds are still mocked end-to-end - the invariant is documented policy + cap logic, not a live bank feed</t>
+          <t>Refund CALCULATION is real and computed (server/domain/refund.ts, since 2026-08-19) - statutory entitlement, party-scaled, shown as a real delta, never a guessed number. What's still mocked is the actual money movement: no live payment/bank integration exists on either side of the ledger. Corrected 2026-08-21 (previously said 'still mocked end-to-end', which was true before 2026-08-19 and is no longer true of the calculation)</t>
         </is>
       </c>
       <c r="H47" s="23" t="n"/>
@@ -2512,27 +2512,27 @@
       </c>
       <c r="C48" s="23" t="inlineStr">
         <is>
-          <t>REAL - I verified this live</t>
+          <t>SUPERSEDED - the cap this row describes was removed 2026-08-19</t>
         </is>
       </c>
       <c r="D48" s="23" t="inlineStr">
         <is>
-          <t>server/engine/simulation.ts overCap branches + policy fare_delta_cap</t>
+          <t>server/notify/templates.ts (four-rung notification ladder), server/engine/simulation.ts settleExpired() delivery check (2026-08-21)</t>
         </is>
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
-          <t>Trigger a recovery whose plan exceeds the Rs 25,000 cap, on any consent tier</t>
+          <t>Trigger a recovery and let the window expire with all notification channels unreachable</t>
         </is>
       </c>
       <c r="F48" s="23" t="inlineStr">
         <is>
-          <t>Engine stops BEFORE anything is charged, explains, hands over</t>
+          <t>As of 2026-08-21: the engine now REQUIRES confirmed rung-3 delivery before an unattended spend proceeds (one 5-min grace retry, then hands over to a human rather than booking blind). It does NOT stop on AMOUNT any more - there is no cap</t>
         </is>
       </c>
       <c r="G48" s="23" t="inlineStr">
         <is>
-          <t>Cap is checked on approve, autopilot AND silent-timeout - even explicit approval cannot pass it</t>
+          <t>Corrected 2026-08-21 - this row was the single most dangerous stale claim in the sheet: it told a reader a Rs 25,000 spend ceiling was enforced on every path, when the cap was removed 2026-08-19 and, until today, delivery wasn't even checked. server/policy/index.ts (12 real policy rules incl. exposure_cap_exceeded) exists but is STILL NOT WIRED into any live route - do not cite it as an active safeguard</t>
         </is>
       </c>
       <c r="H48" s="23" t="n"/>
@@ -3295,27 +3295,27 @@
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t>Covered - per-transaction cap (MyCa, Rs 25,000) is enforced before ANY spend path: approve, autopilot, and silent timeout all check it</t>
+          <t>Partial - the Rs 25,000 per-transaction CAP was removed 2026-08-19 (a stranded member seeing their only seat home refused as 'over your cap' was judged worse than the risk). What replaced it: a four-rung notification ladder, and (2026-08-21) a REQUIRED delivery check before an unattended spend proceeds - undelivered gets one 5-min grace retry, then hands to a human rather than booking blind. There is no longer an amount-based stop</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>server/myca.ts, simulation.ts (overCap branches)</t>
+          <t>server/notify/templates.ts (ladder), server/engine/simulation.ts settleExpired() (delivery check, 2026-08-21), documentation/design/03-action-policy.md §10</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
         <is>
-          <t>Trigger a recovery whose plan costs more than the cap and read the note</t>
+          <t>Trigger a recovery with a large delta and every notification channel unreachable; the engine should hand over to /ops rather than book, but will book a large amount if notifications DO get through and the member stays silent</t>
         </is>
       </c>
       <c r="H13" s="26" t="inlineStr">
         <is>
-          <t>Covered</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
-          <t>The cap is the card limit, not a preference - even explicit approval cannot pass it</t>
+          <t>Corrected 2026-08-21 (previously said the cap was enforced - it is not, since 2026-08-19). A member's own stated budget (from free-text intent) is applied as a preference, not a system-imposed ceiling. server/policy/index.ts has a real exposure_cap_exceeded rule but is NOT wired into any live route</t>
         </is>
       </c>
     </row>
@@ -3875,32 +3875,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Know that everything is charged to my Amex and anything refunded comes back to that same card - and that the system stops before spending past my cap</t>
+          <t>Know that everything is charged to my Amex and anything refunded comes back to that same card - and that the system won't book a large unattended charge without confirming I was actually told first</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Covered - payment routing invariant: all spend on the member's Amex card, all refunds to the same card; per-transaction cap checked on every spend path (approve, autopilot, silent timeout), so the card can never go negative from this flow</t>
+          <t>Partial - the routing invariant is real (all spend and all refunds route through the same card), but it is now enforced by INFORMED CONSENT rather than a hard ceiling. The Rs 25,000 per-transaction cap was removed 2026-08-19. As of 2026-08-21, an unattended spend REQUIRES a confirmed notification delivery first (one grace retry, then hands to a human) - but a member who DOES receive the notification and stays silent will be charged whatever amount was named, with no cap</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>documentation/design/03-action-policy.md §10 (new 2026-08-18), server/engine/simulation.ts overCap branches</t>
+          <t>documentation/design/03-action-policy.md §10 (updated 2026-08-19/21), server/engine/simulation.ts settleExpired()</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Trigger a recovery over the Rs 25,000 cap on /ops and read the explanation</t>
+          <t>Trigger a recovery on /ops with every notification channel unreachable and confirm it hands to a human rather than booking; separately, trigger one with channels reachable and confirm no cap blocks a large amount</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Covered</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Policy written up as §10; cap enforcement is real, refunds still mocked end-to-end</t>
+          <t>Corrected 2026-08-21 (previously claimed cap enforcement, which stopped being true 2026-08-19). Refund calculation is real (server/domain/refund.ts) though live payment settlement remains fully mocked on both sides</t>
         </is>
       </c>
     </row>
